--- a/resources/templates/education/education.xlsx
+++ b/resources/templates/education/education.xlsx
@@ -15,15 +15,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
-  <si>
-    <t>institution</t>
-  </si>
-  <si>
-    <t>program</t>
-  </si>
-  <si>
-    <t>specialty</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
+  <si>
+    <t>institution_ka</t>
+  </si>
+  <si>
+    <t>institution_en</t>
+  </si>
+  <si>
+    <t>program_ka</t>
+  </si>
+  <si>
+    <t>program_en</t>
+  </si>
+  <si>
+    <t>specialty_ka</t>
+  </si>
+  <si>
+    <t>specialty_en</t>
   </si>
   <si>
     <t>started_at</t>
@@ -369,10 +378,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -387,6 +396,15 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
